--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.89334569760836</v>
+        <v>5.832668675861359</v>
       </c>
       <c r="D2" t="n">
-        <v>53.14178605800392</v>
+        <v>8.635540234425639</v>
       </c>
       <c r="E2" t="n">
-        <v>17.66499687091017</v>
+        <v>2.870561991522902</v>
       </c>
       <c r="F2" t="n">
-        <v>17.50348627580335</v>
+        <v>2.844316519818044</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9.362697221903952</v>
+        <v>1.521438298559392</v>
       </c>
       <c r="D3" t="n">
-        <v>45.72736078152406</v>
+        <v>7.430696126997659</v>
       </c>
       <c r="E3" t="n">
-        <v>17.66499687091017</v>
+        <v>2.870561991522902</v>
       </c>
       <c r="F3" t="n">
-        <v>17.50348627580335</v>
+        <v>2.844316519818044</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.14482300479487</v>
+        <v>5.061033738279167</v>
       </c>
       <c r="D4" t="n">
-        <v>39.14175359141935</v>
+        <v>6.360534958605644</v>
       </c>
       <c r="E4" t="n">
-        <v>17.66499687091017</v>
+        <v>2.870561991522902</v>
       </c>
       <c r="F4" t="n">
-        <v>17.50348627580335</v>
+        <v>2.844316519818044</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.95023887191543</v>
+        <v>2.104413816686258</v>
       </c>
       <c r="D5" t="n">
-        <v>43.26044971013599</v>
+        <v>7.029823077897099</v>
       </c>
       <c r="E5" t="n">
-        <v>17.66499687091017</v>
+        <v>2.870561991522902</v>
       </c>
       <c r="F5" t="n">
-        <v>17.50348627580335</v>
+        <v>2.844316519818044</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.79979647782733</v>
+        <v>7.117466927646941</v>
       </c>
       <c r="D6" t="n">
-        <v>20.69703932118296</v>
+        <v>3.363268889692231</v>
       </c>
       <c r="E6" t="n">
-        <v>17.66499687091017</v>
+        <v>2.870561991522902</v>
       </c>
       <c r="F6" t="n">
-        <v>17.50348627580335</v>
+        <v>2.844316519818044</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.21711606097819</v>
+        <v>6.697781359908955</v>
       </c>
       <c r="D7" t="n">
-        <v>20.88857689331897</v>
+        <v>3.394393745164332</v>
       </c>
       <c r="E7" t="n">
-        <v>17.66499687091017</v>
+        <v>2.870561991522902</v>
       </c>
       <c r="F7" t="n">
-        <v>17.50348627580335</v>
+        <v>2.844316519818044</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.07118609867679</v>
+        <v>4.561567741034978</v>
       </c>
       <c r="D8" t="n">
-        <v>11.2276407742398</v>
+        <v>1.824491625813967</v>
       </c>
       <c r="E8" t="n">
-        <v>17.66499687091017</v>
+        <v>2.870561991522902</v>
       </c>
       <c r="F8" t="n">
-        <v>17.50348627580335</v>
+        <v>2.844316519818044</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.39199464354676</v>
+        <v>2.338699129576348</v>
       </c>
       <c r="D9" t="n">
-        <v>14.26486081442568</v>
+        <v>2.318039882344173</v>
       </c>
       <c r="E9" t="n">
-        <v>17.66499687091017</v>
+        <v>2.870561991522902</v>
       </c>
       <c r="F9" t="n">
-        <v>17.50348627580335</v>
+        <v>2.844316519818044</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.90924302670503</v>
+        <v>2.585251991839567</v>
       </c>
       <c r="D10" t="n">
-        <v>16.71856794662362</v>
+        <v>2.716767291326338</v>
       </c>
       <c r="E10" t="n">
-        <v>17.66499687091017</v>
+        <v>2.870561991522902</v>
       </c>
       <c r="F10" t="n">
-        <v>17.50348627580335</v>
+        <v>2.844316519818044</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.59700841106153</v>
+        <v>2.697013866797499</v>
       </c>
       <c r="D11" t="n">
-        <v>10.01249219725039</v>
+        <v>1.627029982053189</v>
       </c>
       <c r="E11" t="n">
-        <v>17.66499687091017</v>
+        <v>2.870561991522902</v>
       </c>
       <c r="F11" t="n">
-        <v>17.50348627580335</v>
+        <v>2.844316519818044</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>71.77724030739382</v>
+        <v>11.6638015499515</v>
       </c>
       <c r="D12" t="n">
-        <v>61.40309725271844</v>
+        <v>9.978003303566746</v>
       </c>
       <c r="E12" t="n">
-        <v>17.66499687091017</v>
+        <v>2.870561991522902</v>
       </c>
       <c r="F12" t="n">
-        <v>17.50348627580335</v>
+        <v>2.844316519818044</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
